--- a/examples/imports/sample-works.xlsx
+++ b/examples/imports/sample-works.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="作品" sheetId="1" r:id="R62a585524c5f454a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="作品" sheetId="1" r:id="R1322901af33043fa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -39,7 +39,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="6">
+  <x:cellXfs count="7">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -50,6 +50,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -310,76 +311,78 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="5" t="str">
-        <x:v>DEMO-IMPORT-003</x:v>
+        <x:v>LX-408</x:v>
       </x:c>
       <x:c r="B2" s="5" t="str">
-        <x:v>星降る午後</x:v>
+        <x:v>晨光笔记</x:v>
       </x:c>
       <x:c r="C2" s="5" t="str">
-        <x:v>星降る午後</x:v>
+        <x:v>朝のノート</x:v>
       </x:c>
       <x:c r="D2" s="5" t="str">
-        <x:v>2026-08-21</x:v>
+        <x:v>2026-09-05</x:v>
       </x:c>
       <x:c r="E2" s="5" t="n">
         <x:v>118</x:v>
       </x:c>
       <x:c r="F2" s="5" t="str">
-        <x:v>星野みづき|白石りん</x:v>
+        <x:v>立花りな</x:v>
       </x:c>
       <x:c r="G2" s="5" t="str">
         <x:v>架空監督A</x:v>
       </x:c>
       <x:c r="H2" s="5" t="str">
-        <x:v>Aurora Works</x:v>
+        <x:v>ルーメン・フィクスチャー</x:v>
       </x:c>
       <x:c r="I2" s="5" t="str">
-        <x:v>Aurora Label</x:v>
+        <x:v>LX テストレーベル</x:v>
       </x:c>
       <x:c r="J2" s="5" t="str">
-        <x:v>夏の記憶</x:v>
+        <x:v>ビジュアル・ノーツ</x:v>
       </x:c>
       <x:c r="K2" s="5" t="str">
-        <x:v>ドラマ|制服</x:v>
+        <x:v>ドラマ|OL</x:v>
       </x:c>
       <x:c r="L2" s="5" t="str">
-        <x:v>待整理</x:v>
+        <x:v>要確認</x:v>
       </x:c>
       <x:c r="M2" s="5" t="str">
-        <x:v>co_starring</x:v>
+        <x:v>image_video</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="5" t="str">
-        <x:v>DEMO-IMPORT-004</x:v>
+        <x:v>LX-409</x:v>
       </x:c>
       <x:c r="B3" s="5" t="str">
-        <x:v>静かな海辺</x:v>
+        <x:v>两人的黄昏</x:v>
       </x:c>
       <x:c r="C3" s="5" t="str">
-        <x:v>静かな海辺</x:v>
+        <x:v>ふたりの夕暮れ</x:v>
       </x:c>
       <x:c r="D3" s="5" t="str">
-        <x:v>2026-08-28</x:v>
+        <x:v>2026-09-06</x:v>
       </x:c>
       <x:c r="E3" s="5" t="n">
         <x:v>96</x:v>
       </x:c>
       <x:c r="F3" s="5" t="str">
-        <x:v>白石りん</x:v>
+        <x:v>水野あいこ|立花りな</x:v>
       </x:c>
       <x:c r="G3" s="5" t="str">
         <x:v>架空監督B</x:v>
       </x:c>
       <x:c r="H3" s="5" t="str">
-        <x:v>North Studio</x:v>
+        <x:v>ルーメン・フィクスチャー</x:v>
       </x:c>
       <x:c r="I3" s="5" t="str">
-        <x:v>North Label</x:v>
-      </x:c>
-      <x:c r="J3" s="5" t="str"/>
+        <x:v>LX テストレーベル</x:v>
+      </x:c>
+      <x:c r="J3" s="5" t="str">
+        <x:v>ビジュアル・ノーツ</x:v>
+      </x:c>
       <x:c r="K3" s="5" t="str">
-        <x:v>イメージ|海辺</x:v>
+        <x:v>ドラマ|スレンダー</x:v>
       </x:c>
       <x:c r="L3" s="5" t="str">
         <x:v>お気に入り</x:v>
